--- a/channel/products/rat-race-escape-planner/Rat-Race-Escape-Planner.xlsx
+++ b/channel/products/rat-race-escape-planner/Rat-Race-Escape-Planner.xlsx
@@ -1427,11 +1427,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="93365701"/>
-        <c:axId val="46833287"/>
+        <c:axId val="30425755"/>
+        <c:axId val="44964645"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="93365701"/>
+        <c:axId val="30425755"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1463,7 +1463,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46833287"/>
+        <c:crossAx val="44964645"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1471,7 +1471,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46833287"/>
+        <c:axId val="44964645"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1513,7 +1513,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93365701"/>
+        <c:crossAx val="30425755"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/channel/products/rat-race-escape-planner/Rat-Race-Escape-Planner.xlsx
+++ b/channel/products/rat-race-escape-planner/Rat-Race-Escape-Planner.xlsx
@@ -1427,11 +1427,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="30425755"/>
-        <c:axId val="44964645"/>
+        <c:axId val="61278214"/>
+        <c:axId val="68041132"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="30425755"/>
+        <c:axId val="61278214"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1463,7 +1463,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44964645"/>
+        <c:crossAx val="68041132"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1471,7 +1471,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44964645"/>
+        <c:axId val="68041132"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1513,7 +1513,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30425755"/>
+        <c:crossAx val="61278214"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1943,7 +1943,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2229,7 +2229,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2552,7 +2552,7 @@
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -2744,7 +2744,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3840,7 +3840,7 @@
   </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4132,7 +4132,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
